--- a/public/downloads/DStructure2024.xlsx
+++ b/public/downloads/DStructure2024.xlsx
@@ -8,30 +8,32 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="NequIP-OAM-L" sheetId="12" r:id="rId12"/>
-    <sheet name="ORB-v3" sheetId="13" r:id="rId13"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="17" r:id="rId17"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="NequIP-OAM-L" sheetId="14" r:id="rId14"/>
+    <sheet name="ORB-v3" sheetId="15" r:id="rId15"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="19" r:id="rId19"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -63,10 +65,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -171,13 +173,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>C6H6O4</t>
   </si>
   <si>
-    <t>H</t>
+    <t>C6H8O4</t>
   </si>
   <si>
-    <t>C6H8O4</t>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -663,10 +686,10 @@
         <v>6</v>
       </c>
       <c r="N3" s="5">
-        <v>17.02858424186707</v>
+        <v>17028.58424186707</v>
       </c>
       <c r="O3" s="4">
-        <v>0.04469444682904741</v>
+        <v>44.69444682904741</v>
       </c>
       <c r="P3" s="5">
         <v>381</v>
@@ -713,10 +736,10 @@
         <v>6</v>
       </c>
       <c r="N4" s="5">
-        <v>15.02969288825989</v>
+        <v>15029.69288825989</v>
       </c>
       <c r="O4" s="4">
-        <v>0.03913982522984346</v>
+        <v>39.13982522984346</v>
       </c>
       <c r="P4" s="5">
         <v>384</v>
@@ -763,10 +786,10 @@
         <v>6</v>
       </c>
       <c r="N5" s="5">
-        <v>27.13232636451721</v>
+        <v>27132.32636451721</v>
       </c>
       <c r="O5" s="4">
-        <v>0.08505431462231101</v>
+        <v>85.05431462231101</v>
       </c>
       <c r="P5" s="5">
         <v>319</v>
@@ -813,10 +836,10 @@
         <v>6</v>
       </c>
       <c r="N6" s="5">
-        <v>37.3558669090271</v>
+        <v>37355.8669090271</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09362372658904035</v>
+        <v>93.62372658904034</v>
       </c>
       <c r="P6" s="5">
         <v>399</v>
@@ -863,10 +886,10 @@
         <v>6</v>
       </c>
       <c r="N7" s="5">
-        <v>27.39126396179199</v>
+        <v>27391.26396179199</v>
       </c>
       <c r="O7" s="4">
-        <v>0.3043473773532444</v>
+        <v>304.3473773532443</v>
       </c>
       <c r="P7" s="5">
         <v>90</v>
@@ -913,10 +936,10 @@
         <v>6</v>
       </c>
       <c r="N8" s="5">
-        <v>7.069808959960938</v>
+        <v>7069.808959960938</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02873906081284934</v>
+        <v>28.73906081284934</v>
       </c>
       <c r="P8" s="5">
         <v>246</v>
@@ -963,10 +986,10 @@
         <v>6</v>
       </c>
       <c r="N9" s="5">
-        <v>17.48841142654419</v>
+        <v>17488.41142654419</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03818430442476897</v>
+        <v>38.18430442476897</v>
       </c>
       <c r="P9" s="5">
         <v>458</v>
@@ -1013,10 +1036,10 @@
         <v>6</v>
       </c>
       <c r="N10" s="5">
-        <v>10.93423914909363</v>
+        <v>10934.23914909363</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1012429550842003</v>
+        <v>101.2429550842002</v>
       </c>
       <c r="P10" s="5">
         <v>108</v>
@@ -1063,10 +1086,10 @@
         <v>6</v>
       </c>
       <c r="N11" s="5">
-        <v>19.2885217666626</v>
+        <v>19288.5217666626</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05102783536154126</v>
+        <v>51.02783536154126</v>
       </c>
       <c r="P11" s="5">
         <v>378</v>
@@ -1113,10 +1136,10 @@
         <v>6</v>
       </c>
       <c r="N12" s="5">
-        <v>8.453175067901611</v>
+        <v>8453.175067901611</v>
       </c>
       <c r="O12" s="4">
-        <v>0.04775805123108255</v>
+        <v>47.75805123108255</v>
       </c>
       <c r="P12" s="5">
         <v>177</v>
@@ -1163,10 +1186,10 @@
         <v>6</v>
       </c>
       <c r="N13" s="5">
-        <v>5.663686037063599</v>
+        <v>5663.686037063599</v>
       </c>
       <c r="O13" s="4">
-        <v>0.02860447493466464</v>
+        <v>28.60447493466464</v>
       </c>
       <c r="P13" s="5">
         <v>198</v>
@@ -1213,10 +1236,10 @@
         <v>6</v>
       </c>
       <c r="N14" s="5">
-        <v>17.62213659286499</v>
+        <v>17622.13659286499</v>
       </c>
       <c r="O14" s="4">
-        <v>0.07077163290307226</v>
+        <v>70.77163290307226</v>
       </c>
       <c r="P14" s="5">
         <v>249</v>
@@ -1263,10 +1286,10 @@
         <v>6</v>
       </c>
       <c r="N15" s="5">
-        <v>106.2127158641815</v>
+        <v>106212.7158641815</v>
       </c>
       <c r="O15" s="4">
-        <v>0.406945271510274</v>
+        <v>406.945271510274</v>
       </c>
       <c r="P15" s="5">
         <v>261</v>
@@ -1313,10 +1336,10 @@
         <v>6</v>
       </c>
       <c r="N16" s="5">
-        <v>65.80700898170471</v>
+        <v>65807.00898170471</v>
       </c>
       <c r="O16" s="4">
-        <v>0.4062161048253377</v>
+        <v>406.2161048253377</v>
       </c>
       <c r="P16" s="5">
         <v>162</v>
@@ -1363,10 +1386,10 @@
         <v>6</v>
       </c>
       <c r="N17" s="5">
-        <v>25.3333203792572</v>
+        <v>25333.3203792572</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09279604534526448</v>
+        <v>92.79604534526447</v>
       </c>
       <c r="P17" s="5">
         <v>273</v>
@@ -1413,10 +1436,10 @@
         <v>6</v>
       </c>
       <c r="N18" s="5">
-        <v>37.92539191246033</v>
+        <v>37925.39191246033</v>
       </c>
       <c r="O18" s="4">
-        <v>0.09341229535088751</v>
+        <v>93.4122953508875</v>
       </c>
       <c r="P18" s="5">
         <v>406</v>
@@ -1444,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1455,9 +1478,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1491,8 +1520,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1514,25 +1551,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.03434322771667553</v>
+        <v>0.7350895385189915</v>
       </c>
       <c r="C3" s="4">
-        <v>0.03434322771667553</v>
+        <v>0.7350895385189915</v>
       </c>
       <c r="D3" s="4">
-        <v>0.003245254873434078</v>
+        <v>0.775873747617311</v>
       </c>
       <c r="E3" s="4">
-        <v>97.04081632653062</v>
+        <v>95.35714285714286</v>
       </c>
       <c r="F3" s="4">
-        <v>98.7248322147651</v>
+        <v>97.61744966442953</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1555,25 +1610,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7350895385189915</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7350895385189915</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.00741922665233119</v>
+        <v>0.6213705837912613</v>
       </c>
       <c r="C4" s="4">
-        <v>0.00741922665233119</v>
+        <v>0.6213705837912613</v>
       </c>
       <c r="D4" s="4">
-        <v>0.0107022019994929</v>
+        <v>0.573897400253415</v>
       </c>
       <c r="E4" s="4">
-        <v>94.59183673469387</v>
+        <v>93.31632653061224</v>
       </c>
       <c r="F4" s="4">
-        <v>98.10402684563758</v>
+        <v>92.48322147651007</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -1596,25 +1667,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6213705837912613</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6213705837912613</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1194897799343693</v>
+        <v>0.07067377744857595</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1194897799343693</v>
+        <v>0.07067377744857595</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1098879601679954</v>
+        <v>0.08444090902145263</v>
       </c>
       <c r="E5" s="4">
-        <v>97.09183673469387</v>
+        <v>94.64285714285714</v>
       </c>
       <c r="F5" s="4">
-        <v>98.84228187919463</v>
+        <v>97.90268456375838</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -1637,9 +1724,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07067377744857595</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07067377744857595</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1650,6 +1753,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1657,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1668,9 +1772,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1704,8 +1814,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1727,76 +1845,110 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.361131575773868</v>
+        <v>0.4827467896319035</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5809573592738388</v>
+        <v>0.4827467896319035</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2626723040691559</v>
+        <v>0.2685434306798697</v>
       </c>
       <c r="E3" s="4">
-        <v>93.41836734693878</v>
+        <v>91.39455782312925</v>
       </c>
       <c r="F3" s="4">
-        <v>82.86353467561543</v>
+        <v>88.8646532438479</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4827467896319035</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4827467896319035</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6589368396806492</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2997854586401729</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4749417359027177</v>
+      </c>
+      <c r="E4" s="4">
+        <v>88.9795918367347</v>
+      </c>
+      <c r="F4" s="4">
+        <v>81.92953020134229</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.07946702906824044</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.07946702906824044</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.07670359707904595</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.62244897959184</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.4496644295302</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
       <c r="J4" s="5">
         <v>0</v>
       </c>
@@ -1809,34 +1961,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6589368396806492</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2997854586401729</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4819853565843744</v>
+        <v>0.3131931762478644</v>
       </c>
       <c r="C5" s="4">
-        <v>0.02204595955564059</v>
+        <v>0.3131931762478644</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2857251221331865</v>
+        <v>0.3170397768123223</v>
       </c>
       <c r="E5" s="4">
-        <v>91.27551020408163</v>
+        <v>92.34693877551021</v>
       </c>
       <c r="F5" s="4">
-        <v>76.22483221476509</v>
+        <v>97.26510067114094</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1850,9 +2018,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3131931762478644</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3131931762478644</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1863,6 +2047,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1870,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1881,9 +2066,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1917,8 +2108,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1940,25 +2139,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6621317866693062</v>
+        <v>0.03434322771667553</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6621317866693062</v>
+        <v>0.03434322771667553</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7358154224788223</v>
+        <v>0.003245254873434078</v>
       </c>
       <c r="E3" s="4">
-        <v>96.93877551020408</v>
+        <v>97.04081632653062</v>
       </c>
       <c r="F3" s="4">
-        <v>97.26510067114094</v>
+        <v>98.7248322147651</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1981,25 +2198,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03434322771667553</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03434322771667553</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.072479327778467</v>
+        <v>0.1194897799343693</v>
       </c>
       <c r="C4" s="4">
-        <v>0.072479327778467</v>
+        <v>0.1194897799343693</v>
       </c>
       <c r="D4" s="4">
-        <v>0.07276667796591596</v>
+        <v>0.1098879601679954</v>
       </c>
       <c r="E4" s="4">
-        <v>95.81632653061224</v>
+        <v>97.09183673469387</v>
       </c>
       <c r="F4" s="4">
-        <v>98.6241610738255</v>
+        <v>98.84228187919463</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2022,25 +2255,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1194897799343693</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1194897799343693</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6680510631969838</v>
+        <v>0.00741922665233119</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6680510631969838</v>
+        <v>0.00741922665233119</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6716714554124792</v>
+        <v>0.0107022019994929</v>
       </c>
       <c r="E5" s="4">
-        <v>96.42857142857143</v>
+        <v>94.59183673469387</v>
       </c>
       <c r="F5" s="4">
-        <v>96.91275167785236</v>
+        <v>98.10402684563758</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2063,9 +2312,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.00741922665233119</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.00741922665233119</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2076,6 +2341,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2083,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2094,9 +2360,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2130,8 +2402,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2153,34 +2433,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5011439137946923</v>
+        <v>0.361131575773868</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5011439137946923</v>
+        <v>0.5809573592738388</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4516524066082184</v>
+        <v>0.2626723040691559</v>
       </c>
       <c r="E3" s="4">
-        <v>96.32653061224489</v>
+        <v>93.41836734693878</v>
       </c>
       <c r="F3" s="4">
-        <v>98.13199105145415</v>
+        <v>82.86353467561543</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2194,34 +2492,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.361131575773868</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5809573592738388</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.02928242582021312</v>
+        <v>0.4819853565843744</v>
       </c>
       <c r="C4" s="4">
-        <v>0.02928242582021312</v>
+        <v>0.02204595955564059</v>
       </c>
       <c r="D4" s="4">
-        <v>0.03475909329486626</v>
+        <v>0.2857251221331865</v>
       </c>
       <c r="E4" s="4">
-        <v>93.65646258503402</v>
+        <v>91.27551020408163</v>
       </c>
       <c r="F4" s="4">
-        <v>97.81319910514543</v>
+        <v>76.22483221476509</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2235,25 +2549,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4819853565843744</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.02204595955564059</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2981408607818707</v>
+        <v>0.07946702906824044</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2981408607818707</v>
+        <v>0.07946702906824044</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2590517943707198</v>
+        <v>0.07670359707904595</v>
       </c>
       <c r="E5" s="4">
-        <v>95.66326530612245</v>
+        <v>93.62244897959184</v>
       </c>
       <c r="F5" s="4">
-        <v>96.28635346756151</v>
+        <v>97.4496644295302</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2276,9 +2606,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07946702906824044</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07946702906824044</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2289,6 +2635,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2296,7 +2643,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2307,9 +2654,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2343,8 +2696,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2366,25 +2727,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4448980937133342</v>
+        <v>0.6621317866693062</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4448980937133342</v>
+        <v>0.6621317866693062</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4830247174152191</v>
+        <v>0.7358154224788223</v>
       </c>
       <c r="E3" s="4">
-        <v>98.21428571428571</v>
+        <v>96.93877551020408</v>
       </c>
       <c r="F3" s="4">
-        <v>98.65771812080537</v>
+        <v>97.26510067114094</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2407,25 +2786,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6621317866693062</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6621317866693062</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.210453835494576</v>
+        <v>0.6680510631969838</v>
       </c>
       <c r="C4" s="4">
-        <v>0.210453835494576</v>
+        <v>0.6680510631969838</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2092504987819268</v>
+        <v>0.6716714554124792</v>
       </c>
       <c r="E4" s="4">
-        <v>97.85714285714286</v>
+        <v>96.42857142857143</v>
       </c>
       <c r="F4" s="4">
-        <v>99.26174496644295</v>
+        <v>96.91275167785236</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2448,34 +2843,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6680510631969838</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6680510631969838</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8503448391801811</v>
+        <v>0.072479327778467</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7005554355244925</v>
+        <v>0.072479327778467</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7971692139300615</v>
+        <v>0.07276667796591596</v>
       </c>
       <c r="E5" s="4">
-        <v>95.15306122448979</v>
+        <v>95.81632653061224</v>
       </c>
       <c r="F5" s="4">
-        <v>85.01677852348993</v>
+        <v>98.6241610738255</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2489,9 +2900,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.072479327778467</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.072479327778467</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2502,6 +2929,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2509,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2520,9 +2948,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2556,8 +2990,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2579,25 +3021,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8462030473316702</v>
+        <v>0.5011439137946923</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8462030473316702</v>
+        <v>0.5011439137946923</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8470524539106918</v>
+        <v>0.4516524066082184</v>
       </c>
       <c r="E3" s="4">
-        <v>93.82653061224489</v>
+        <v>96.32653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>94.8993288590604</v>
+        <v>98.13199105145415</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2620,25 +3080,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5011439137946923</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5011439137946923</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1552176873379665</v>
+        <v>0.2981408607818707</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1552176873379665</v>
+        <v>0.2981408607818707</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1426930537121223</v>
+        <v>0.2590517943707198</v>
       </c>
       <c r="E4" s="4">
-        <v>94.08163265306122</v>
+        <v>95.66326530612245</v>
       </c>
       <c r="F4" s="4">
-        <v>97.3993288590604</v>
+        <v>96.28635346756151</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2661,25 +3137,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2981408607818707</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2981408607818707</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7841766755299489</v>
+        <v>0.02928242582021312</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7841766755299489</v>
+        <v>0.02928242582021312</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7866749709455689</v>
+        <v>0.03475909329486626</v>
       </c>
       <c r="E5" s="4">
-        <v>93.31632653061224</v>
+        <v>93.65646258503402</v>
       </c>
       <c r="F5" s="4">
-        <v>92.34899328859061</v>
+        <v>97.81319910514543</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2702,9 +3194,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.02928242582021312</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02928242582021312</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2715,6 +3223,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2722,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2733,9 +3242,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2769,8 +3284,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2792,25 +3315,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8623860321473558</v>
+        <v>0.4448980937133342</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8623860321473558</v>
+        <v>0.4448980937133342</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8855477581872719</v>
+        <v>0.4830247174152191</v>
       </c>
       <c r="E3" s="4">
-        <v>97.44897959183673</v>
+        <v>98.21428571428571</v>
       </c>
       <c r="F3" s="4">
-        <v>98.59060402684564</v>
+        <v>98.65771812080537</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2833,34 +3374,50 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4448980937133342</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4448980937133342</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1805965166294072</v>
+        <v>0.8503448391801811</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1805965166294072</v>
+        <v>0.7005554355244925</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1823476741416812</v>
+        <v>0.7971692139300615</v>
       </c>
       <c r="E4" s="4">
-        <v>95.20408163265306</v>
+        <v>95.15306122448979</v>
       </c>
       <c r="F4" s="4">
-        <v>98.40604026845638</v>
+        <v>85.01677852348993</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2874,25 +3431,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8503448391801811</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7005554355244925</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6960201998063553</v>
+        <v>0.210453835494576</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6960201998063553</v>
+        <v>0.210453835494576</v>
       </c>
       <c r="D5" s="4">
-        <v>0.698617463747496</v>
+        <v>0.2092504987819268</v>
       </c>
       <c r="E5" s="4">
-        <v>96.4795918367347</v>
+        <v>97.85714285714286</v>
       </c>
       <c r="F5" s="4">
-        <v>95.57046979865771</v>
+        <v>99.26174496644295</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -2915,9 +3488,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.210453835494576</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.210453835494576</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2928,6 +3517,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2935,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2946,9 +3536,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2982,8 +3578,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3005,25 +3609,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8284714082826667</v>
+        <v>0.8462030473316702</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8284714082826667</v>
+        <v>0.8462030473316702</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8319309939496407</v>
+        <v>0.8470524539106918</v>
       </c>
       <c r="E3" s="4">
-        <v>93.41836734693878</v>
+        <v>93.82653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>95.20134228187919</v>
+        <v>94.8993288590604</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -3046,25 +3668,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8462030473316702</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8462030473316702</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1438052536995258</v>
+        <v>0.7841766755299489</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1438052536995258</v>
+        <v>0.7841766755299489</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1311563810007499</v>
+        <v>0.7866749709455689</v>
       </c>
       <c r="E4" s="4">
-        <v>93.62244897959184</v>
+        <v>93.31632653061224</v>
       </c>
       <c r="F4" s="4">
-        <v>97.28187919463087</v>
+        <v>92.34899328859061</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -3087,25 +3725,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7841766755299489</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7841766755299489</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7579905208179269</v>
+        <v>0.1552176873379665</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7579905208179269</v>
+        <v>0.1552176873379665</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7673277800886353</v>
+        <v>0.1426930537121223</v>
       </c>
       <c r="E5" s="4">
-        <v>92.70408163265306</v>
+        <v>94.08163265306122</v>
       </c>
       <c r="F5" s="4">
-        <v>90.78859060402685</v>
+        <v>97.3993288590604</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -3128,9 +3782,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1552176873379665</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1552176873379665</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3141,6 +3811,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3148,7 +3819,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3159,9 +3830,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3195,8 +3872,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3218,34 +3903,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9058313824948527</v>
+        <v>0.8623860321473558</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8835386859474283</v>
+        <v>0.8623860321473558</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9462374438390952</v>
+        <v>0.8855477581872719</v>
       </c>
       <c r="E3" s="4">
-        <v>95</v>
+        <v>97.44897959183673</v>
       </c>
       <c r="F3" s="4">
-        <v>89.31208053691275</v>
+        <v>98.59060402684564</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -3259,25 +3962,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8623860321473558</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8623860321473558</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
-        <v>0.04222053503693246</v>
+        <v>0.6960201998063553</v>
       </c>
       <c r="C4" s="4">
-        <v>0.04222053503693246</v>
+        <v>0.6960201998063553</v>
       </c>
       <c r="D4" s="4">
-        <v>0.04187177516058682</v>
+        <v>0.698617463747496</v>
       </c>
       <c r="E4" s="4">
-        <v>95.61224489795919</v>
+        <v>96.4795918367347</v>
       </c>
       <c r="F4" s="4">
-        <v>98.55704697986577</v>
+        <v>95.57046979865771</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -3300,34 +4019,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6960201998063553</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6960201998063553</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
-        <v>1.381964654466906</v>
+        <v>0.1805965166294072</v>
       </c>
       <c r="C5" s="4">
-        <v>1.62468817882008</v>
+        <v>0.1805965166294072</v>
       </c>
       <c r="D5" s="4">
-        <v>1.534330839474933</v>
+        <v>0.1823476741416812</v>
       </c>
       <c r="E5" s="4">
-        <v>89.43877551020408</v>
+        <v>95.20408163265306</v>
       </c>
       <c r="F5" s="4">
-        <v>73.55704697986577</v>
+        <v>98.40604026845638</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3341,9 +4076,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1805965166294072</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1805965166294072</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3354,12 +4105,1508 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.8284714082826667</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.8284714082826667</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.8319309939496407</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.41836734693878</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.20134228187919</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8284714082826667</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8284714082826667</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7579905208179269</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7579905208179269</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7673277800886353</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.70408163265306</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.78859060402685</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7579905208179269</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7579905208179269</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1438052536995258</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1438052536995258</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1311563810007499</v>
+      </c>
+      <c r="E5" s="4">
+        <v>93.62244897959184</v>
+      </c>
+      <c r="F5" s="4">
+        <v>97.28187919463087</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1438052536995258</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1438052536995258</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D3" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.464495693944301</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.8428279782361633</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.507330629910228</v>
+      </c>
+      <c r="K3" s="4">
+        <v>94.03061224489795</v>
+      </c>
+      <c r="L3" s="4">
+        <v>92.12527964205779</v>
+      </c>
+      <c r="M3" s="5">
+        <v>6</v>
+      </c>
+      <c r="N3" s="5">
+        <v>17028.58424186707</v>
+      </c>
+      <c r="O3" s="4">
+        <v>44.69444682904741</v>
+      </c>
+      <c r="P3" s="5">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C4" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.8877742203264631</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7327960943444112</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.830008644347212</v>
+      </c>
+      <c r="K4" s="4">
+        <v>93.12925170068029</v>
+      </c>
+      <c r="L4" s="4">
+        <v>90.03355704698065</v>
+      </c>
+      <c r="M4" s="5">
+        <v>6</v>
+      </c>
+      <c r="N4" s="5">
+        <v>15029.69288825989</v>
+      </c>
+      <c r="O4" s="4">
+        <v>39.13982522984346</v>
+      </c>
+      <c r="P4" s="5">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3656670173828426</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.3656670173828426</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3730955045247697</v>
+      </c>
+      <c r="K5" s="4">
+        <v>93.04421768707483</v>
+      </c>
+      <c r="L5" s="4">
+        <v>94.05853840417602</v>
+      </c>
+      <c r="M5" s="5">
+        <v>6</v>
+      </c>
+      <c r="N5" s="5">
+        <v>27132.32636451721</v>
+      </c>
+      <c r="O5" s="4">
+        <v>85.05431462231101</v>
+      </c>
+      <c r="P5" s="5">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C6" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.301668130565055</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2148800737354492</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3165921156454298</v>
+      </c>
+      <c r="K6" s="4">
+        <v>89.59750566893425</v>
+      </c>
+      <c r="L6" s="4">
+        <v>89.65510812826371</v>
+      </c>
+      <c r="M6" s="5">
+        <v>6</v>
+      </c>
+      <c r="N6" s="5">
+        <v>37355.8669090271</v>
+      </c>
+      <c r="O6" s="4">
+        <v>93.62372658904034</v>
+      </c>
+      <c r="P6" s="5">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1202350752063144</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1202350752063144</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.118794896686893</v>
+      </c>
+      <c r="K7" s="4">
+        <v>97.78911564625851</v>
+      </c>
+      <c r="L7" s="4">
+        <v>99.04921700223714</v>
+      </c>
+      <c r="M7" s="5">
+        <v>6</v>
+      </c>
+      <c r="N7" s="5">
+        <v>27391.26396179199</v>
+      </c>
+      <c r="O7" s="4">
+        <v>304.3473773532443</v>
+      </c>
+      <c r="P7" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4757112999196096</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.4757112999196096</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4780706856307262</v>
+      </c>
+      <c r="K8" s="4">
+        <v>94.43877551020408</v>
+      </c>
+      <c r="L8" s="4">
+        <v>96.00111856823277</v>
+      </c>
+      <c r="M8" s="5">
+        <v>6</v>
+      </c>
+      <c r="N8" s="5">
+        <v>7069.808959960938</v>
+      </c>
+      <c r="O8" s="4">
+        <v>28.73906081284934</v>
+      </c>
+      <c r="P8" s="5">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C9" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4849589351868057</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3783330780799418</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3535083144649699</v>
+      </c>
+      <c r="K9" s="4">
+        <v>90.90702947845807</v>
+      </c>
+      <c r="L9" s="4">
+        <v>89.35309470544406</v>
+      </c>
+      <c r="M9" s="5">
+        <v>6</v>
+      </c>
+      <c r="N9" s="5">
+        <v>17488.41142654419</v>
+      </c>
+      <c r="O9" s="4">
+        <v>38.18430442476897</v>
+      </c>
+      <c r="P9" s="5">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.05375074476779199</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.05375074476779199</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.04127847234697413</v>
+      </c>
+      <c r="K10" s="4">
+        <v>96.24149659863944</v>
+      </c>
+      <c r="L10" s="4">
+        <v>98.55704697986577</v>
+      </c>
+      <c r="M10" s="5">
+        <v>6</v>
+      </c>
+      <c r="N10" s="5">
+        <v>10934.23914909363</v>
+      </c>
+      <c r="O10" s="4">
+        <v>101.2429550842002</v>
+      </c>
+      <c r="P10" s="5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C11" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.307527987142161</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1904843442414901</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2083670077604628</v>
+      </c>
+      <c r="K11" s="4">
+        <v>92.77210884353744</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.51267710663815</v>
+      </c>
+      <c r="M11" s="5">
+        <v>6</v>
+      </c>
+      <c r="N11" s="5">
+        <v>19288.5217666626</v>
+      </c>
+      <c r="O11" s="4">
+        <v>51.02783536154126</v>
+      </c>
+      <c r="P11" s="5">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.467554059214919</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.467554059214919</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.4934178519524058</v>
+      </c>
+      <c r="K12" s="4">
+        <v>96.39455782312925</v>
+      </c>
+      <c r="L12" s="4">
+        <v>97.6006711409396</v>
+      </c>
+      <c r="M12" s="5">
+        <v>6</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8453.175067901611</v>
+      </c>
+      <c r="O12" s="4">
+        <v>47.75805123108255</v>
+      </c>
+      <c r="P12" s="5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2761890667989254</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2761890667989254</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2484877647579348</v>
+      </c>
+      <c r="K13" s="4">
+        <v>95.21541950113378</v>
+      </c>
+      <c r="L13" s="4">
+        <v>97.41051454138702</v>
+      </c>
+      <c r="M13" s="5">
+        <v>6</v>
+      </c>
+      <c r="N13" s="5">
+        <v>5663.686037063599</v>
+      </c>
+      <c r="O13" s="4">
+        <v>28.60447493466464</v>
+      </c>
+      <c r="P13" s="5">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C14" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.5018989227960304</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4022518587880626</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4964814767090691</v>
+      </c>
+      <c r="K14" s="4">
+        <v>97.0748299319728</v>
+      </c>
+      <c r="L14" s="4">
+        <v>94.31208053691267</v>
+      </c>
+      <c r="M14" s="5">
+        <v>6</v>
+      </c>
+      <c r="N14" s="5">
+        <v>17622.13659286499</v>
+      </c>
+      <c r="O14" s="4">
+        <v>70.77163290307226</v>
+      </c>
+      <c r="P14" s="5">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5951991367331951</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.5951991367331951</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5921401595227943</v>
+      </c>
+      <c r="K15" s="4">
+        <v>93.74149659863944</v>
+      </c>
+      <c r="L15" s="4">
+        <v>94.88255033557063</v>
+      </c>
+      <c r="M15" s="5">
+        <v>6</v>
+      </c>
+      <c r="N15" s="5">
+        <v>106212.7158641815</v>
+      </c>
+      <c r="O15" s="4">
+        <v>406.945271510274</v>
+      </c>
+      <c r="P15" s="5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5796675828610395</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.5796675828610395</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.588837632025483</v>
+      </c>
+      <c r="K16" s="4">
+        <v>96.37755102040816</v>
+      </c>
+      <c r="L16" s="4">
+        <v>97.52237136465322</v>
+      </c>
+      <c r="M16" s="5">
+        <v>6</v>
+      </c>
+      <c r="N16" s="5">
+        <v>65807.00898170471</v>
+      </c>
+      <c r="O16" s="4">
+        <v>406.2161048253377</v>
+      </c>
+      <c r="P16" s="5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.5767557276000398</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5767557276000398</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.5768050516796753</v>
+      </c>
+      <c r="K17" s="4">
+        <v>93.24829931972791</v>
+      </c>
+      <c r="L17" s="4">
+        <v>94.42393736017902</v>
+      </c>
+      <c r="M17" s="5">
+        <v>6</v>
+      </c>
+      <c r="N17" s="5">
+        <v>25333.3203792572</v>
+      </c>
+      <c r="O17" s="4">
+        <v>92.79604534526447</v>
+      </c>
+      <c r="P17" s="5">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C18" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.7766721906662303</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.6481669837103432</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.8408133528248717</v>
+      </c>
+      <c r="K18" s="4">
+        <v>93.3503401360544</v>
+      </c>
+      <c r="L18" s="4">
+        <v>87.14205816555022</v>
+      </c>
+      <c r="M18" s="5">
+        <v>6</v>
+      </c>
+      <c r="N18" s="5">
+        <v>37925.39191246033</v>
+      </c>
+      <c r="O18" s="4">
+        <v>93.4122953508875</v>
+      </c>
+      <c r="P18" s="5">
+        <v>406</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9058313824948527</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.8835386859474283</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9462374438390952</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.31208053691275</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9058313824948527</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.8835386859474283</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.381964654466906</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.62468817882008</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.534330839474933</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.43877551020408</v>
+      </c>
+      <c r="F4" s="4">
+        <v>73.55704697986577</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.381964654466906</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.62468817882008</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.04222053503693246</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.04222053503693246</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.04187177516058682</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.61224489795919</v>
+      </c>
+      <c r="F5" s="4">
+        <v>98.55704697986577</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04222053503693246</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04222053503693246</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4158,9 +6405,808 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>6</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4171,9 +7217,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -4207,8 +7259,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4230,17 +7290,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>2.038051323535115</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>2.101807789700217</v>
       </c>
@@ -4271,75 +7347,105 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>2.038051323535115</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
+        <v>2.061693891423559</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.941000200960033</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2.118296311346853</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>84.73154362416108</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.061693891423559</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.941000200960033</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.2937418668742282</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.2937418668742282</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.3018877886836151</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>94.59183673469387</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>98.08724832214764</v>
       </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2.061693891423559</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.941000200960033</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2.118296311346853</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.5</v>
-      </c>
-      <c r="F5" s="4">
-        <v>84.73154362416108</v>
-      </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4353,9 +7459,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2937418668742282</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2937418668742282</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4366,14 +7488,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4384,9 +7507,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -4420,8 +7549,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4443,10 +7580,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.013925366926117</v>
@@ -4484,75 +7639,107 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.013925366926117</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.013925366926117</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
+        <v>1.363590177302058</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.064515504367392</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.16917086187928</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.59183673469387</v>
+      </c>
+      <c r="F4" s="4">
+        <v>78.03691275167785</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.363590177302058</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.064515504367392</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.2858071167512151</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.2858071167512151</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.3696144113643243</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>95.05102040816327</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>98.15436241610739</v>
       </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.363590177302058</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.064515504367392</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.16917086187928</v>
-      </c>
-      <c r="E5" s="4">
-        <v>89.59183673469387</v>
-      </c>
-      <c r="F5" s="4">
-        <v>78.03691275167785</v>
-      </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4566,9 +7753,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2858071167512151</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2858071167512151</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4579,14 +7782,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4597,9 +7801,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -4633,8 +7843,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4656,10 +7874,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.3930999714843892</v>
@@ -4697,67 +7933,99 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3930999714843892</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3930999714843892</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
+        <v>0.6683952327734914</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6683952327734914</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6363746639258352</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.19387755102041</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.9675615212528</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6683952327734914</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6683952327734914</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.03550584789064715</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.03550584789064715</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.04522569652345965</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>92.80612244897959</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>97.14765100671141</v>
       </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6683952327734914</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6683952327734914</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6363746639258352</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.19387755102041</v>
-      </c>
-      <c r="F5" s="4">
-        <v>90.9675615212528</v>
-      </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
@@ -4779,9 +8047,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03550584789064715</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03550584789064715</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4792,14 +8076,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4810,9 +8095,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -4846,8 +8137,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4869,10 +8168,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.317879729221147</v>
@@ -4910,75 +8227,107 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.317879729221147</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.317879729221147</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
+        <v>0.4006209352550272</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.06563345579697</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3293042236956865</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.80272108843538</v>
+      </c>
+      <c r="F4" s="4">
+        <v>76.51565995525728</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4006209352550272</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06563345579697</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.1865037272189909</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.1865037272189909</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.1922951231105401</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>89.48979591836735</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>95.78859060402685</v>
       </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4006209352550272</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06563345579697</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3293042236956865</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.80272108843538</v>
-      </c>
-      <c r="F5" s="4">
-        <v>76.51565995525728</v>
-      </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4992,9 +8341,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1865037272189909</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1865037272189909</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5005,14 +8370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5023,9 +8389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -5059,8 +8431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5082,10 +8462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.1053278320696904</v>
@@ -5123,67 +8521,99 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1053278320696904</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1053278320696904</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
+        <v>0.2272181143525813</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2272181143525813</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2257046753558427</v>
+      </c>
+      <c r="E4" s="4">
+        <v>98.16326530612245</v>
+      </c>
+      <c r="F4" s="4">
+        <v>99.09395973154362</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2272181143525813</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2272181143525813</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.0281592791966716</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.0281592791966716</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.02469234562946099</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>96.93877551020408</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>98.85906040268456</v>
       </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2272181143525813</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2272181143525813</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2257046753558427</v>
-      </c>
-      <c r="E5" s="4">
-        <v>98.16326530612245</v>
-      </c>
-      <c r="F5" s="4">
-        <v>99.09395973154362</v>
-      </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
@@ -5205,9 +8635,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0281592791966716</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0281592791966716</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5218,432 +8664,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7350895385189915</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7350895385189915</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.775873747617311</v>
-      </c>
-      <c r="E3" s="4">
-        <v>95.35714285714286</v>
-      </c>
-      <c r="F3" s="4">
-        <v>97.61744966442953</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.07067377744857595</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.07067377744857595</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.08444090902145263</v>
-      </c>
-      <c r="E4" s="4">
-        <v>94.64285714285714</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.90268456375838</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6213705837912613</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6213705837912613</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.573897400253415</v>
-      </c>
-      <c r="E5" s="4">
-        <v>93.31632653061224</v>
-      </c>
-      <c r="F5" s="4">
-        <v>92.48322147651007</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4827467896319035</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4827467896319035</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2685434306798697</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.39455782312925</v>
-      </c>
-      <c r="F3" s="4">
-        <v>88.8646532438479</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3131931762478644</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3131931762478644</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3170397768123223</v>
-      </c>
-      <c r="E4" s="4">
-        <v>92.34693877551021</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.26510067114094</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6589368396806492</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2997854586401729</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4749417359027177</v>
-      </c>
-      <c r="E5" s="4">
-        <v>88.9795918367347</v>
-      </c>
-      <c r="F5" s="4">
-        <v>81.92953020134229</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
